--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:22</t>
+    <t xml:space="preserve">2026-09-10 01:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:36</t>
+    <t xml:space="preserve">2026-09-18 11:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:32</t>
+    <t xml:space="preserve">2026-09-23 15:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:37</t>
+    <t xml:space="preserve">2026-10-05 16:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1411,7 +1411,7 @@
         <v>68.51</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>103.12</v>
+        <v>103.13</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>103.17</v>
